--- a/parquet - schema/MetaData.xlsx
+++ b/parquet - schema/MetaData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>June 30, 2024</t>
+          <t>JUNE 30, 2025</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>For the Year Ended June 30, 2024</t>
+          <t>FOR THE YEAR ENDED JUNE 30, 2025</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30-JUN-2024</t>
+          <t>June 30, 2025</t>
         </is>
       </c>
     </row>
@@ -488,81 +488,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>September 30, 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FYE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>For the year ended September 30, 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FYE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>30-SEP-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FYE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>June 30, 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FYE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>For the year ended June 30, 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FYE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>30-JUN-2025</t>
         </is>
